--- a/population-projection/src/main/resources/mortality_tables/RSFSR/RSFSR-MortalityRates-ADH.xlsx
+++ b/population-projection/src/main/resources/mortality_tables/RSFSR/RSFSR-MortalityRates-ADH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-time-progression\src\main\resources\mortality_tables\RSFSR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\population-projection\src\main\resources\mortality_tables\RSFSR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F739FDD-FFBB-4E37-A78A-13714FB17651}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A1EEEE-79C2-495D-8B8E-B1758081E8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2535" yWindow="8865" windowWidth="28980" windowHeight="13020" xr2:uid="{766AE3CE-855B-4024-BC78-E28714A6AB15}"/>
+    <workbookView xWindow="59865" yWindow="4020" windowWidth="38700" windowHeight="14970" xr2:uid="{766AE3CE-855B-4024-BC78-E28714A6AB15}"/>
   </bookViews>
   <sheets>
     <sheet name="Comment" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
   <si>
     <t>Е.М.Андреев, Л.Е.Дарский, Т.Л. Харькова, "Демографическая история России : 1927-1959", НИИ статистики Госкомстата России, Отделение демографии, М. 1998, 167-170</t>
   </si>
@@ -101,7 +101,13 @@
     <t>Возрастные коэффициенты смертности РСФСР (промилле) по АДХ:</t>
   </si>
   <si>
-    <t>Величины приведены в формате "mx", а не "qx" (уточнено в переписке с Е.М. Андреевым).</t>
+    <t xml:space="preserve"> (уточнено в переписке с Е.М. Андреевым).</t>
+  </si>
+  <si>
+    <t>кроме младенческой смертности, которая приведена в формате q0</t>
+  </si>
+  <si>
+    <t>Величины приведены в формате "mx", а не "qx" для x &gt;= 1,</t>
   </si>
 </sst>
 </file>
@@ -179,9 +185,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -219,7 +225,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -325,7 +331,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -467,7 +473,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -475,21 +481,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F59326FF-4098-4940-B01A-41D42783F94B}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
     </row>
@@ -501,9 +517,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08EEC57D-E0AE-4448-8B4D-E6FE6448CC0B}">
   <dimension ref="A1:AB20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -589,7 +605,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -675,7 +691,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -761,7 +777,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -847,7 +863,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -933,7 +949,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -1019,7 +1035,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1105,7 +1121,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1191,7 +1207,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1277,7 +1293,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1363,7 +1379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1449,7 +1465,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1535,7 +1551,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1621,7 +1637,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1707,7 +1723,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1793,7 +1809,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
@@ -1879,7 +1895,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
@@ -1965,7 +1981,7 @@
         <v>62.4</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
@@ -2051,7 +2067,7 @@
         <v>85.7</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
@@ -2137,7 +2153,7 @@
         <v>156.19999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
@@ -2231,9 +2247,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B86946-7746-460C-9ECB-D0E92C2546D8}">
   <dimension ref="A1:AB29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2319,7 +2335,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -2405,7 +2421,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -2491,7 +2507,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -2577,7 +2593,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -2663,7 +2679,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -2749,7 +2765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -2835,7 +2851,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -2921,7 +2937,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -3007,7 +3023,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3093,7 +3109,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -3179,7 +3195,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
@@ -3265,7 +3281,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -3351,7 +3367,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
@@ -3437,7 +3453,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
@@ -3523,7 +3539,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
@@ -3609,7 +3625,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
@@ -3695,7 +3711,7 @@
         <v>37.9</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
@@ -3781,7 +3797,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
@@ -3867,7 +3883,7 @@
         <v>99.6</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
@@ -3953,35 +3969,41 @@
         <v>148.1</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1"/>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1"/>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1"/>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1"/>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>